--- a/ActionMake00/Assets/Resources/Jsons/Excels/ItemData_Template.xlsx
+++ b/ActionMake00/Assets/Resources/Jsons/Excels/ItemData_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JustAction00\ActionMake00\Assets\Resources\Jsons\Excels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ParkSeongJun\JustAction00\ActionMake00\Assets\Resources\Jsons\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1301CA2C-8DDE-4C16-8B18-DAFDDFE56CE1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C342D75C-29C4-46AD-83EF-B1AC4789EF31}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,27 +55,15 @@
     <t>실험소비템</t>
   </si>
   <si>
-    <t>03_Alchemy</t>
-  </si>
-  <si>
     <t>특이한투구</t>
   </si>
   <si>
-    <t>03_plate_helm_E</t>
-  </si>
-  <si>
     <t>일반투구</t>
   </si>
   <si>
-    <t>03_plate_helm_nobg</t>
-  </si>
-  <si>
     <t>집행검</t>
   </si>
   <si>
-    <t>09_Longsword</t>
-  </si>
-  <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -92,10 +80,28 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>08_Mage_Staff_nobg</t>
-  </si>
-  <si>
-    <t>02_Sword_nobg</t>
+    <t>Resources\JsonImageData\08_Mage_Staff_nobg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Resources\JsonImageData\02_Sword_nobg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Resources\JsonImageData\09_Longsword</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Resources\JsonImageDat\03_plate_helm_nobg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Resources\JsonImageData\03_plate_helm_E</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Resources\JsonImageData\03_Alchemy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -448,8 +454,8 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.25" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.25" style="1" bestFit="1" customWidth="1"/>
@@ -473,7 +479,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -481,7 +487,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>8</v>
@@ -498,10 +504,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -518,10 +524,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -538,10 +544,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -558,16 +564,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -578,16 +584,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
